--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
@@ -2207,11 +2207,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="49414882"/>
-        <c:axId val="10597235"/>
+        <c:axId val="58233594"/>
+        <c:axId val="45724715"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="49414882"/>
+        <c:axId val="58233594"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2241,7 +2241,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10597235"/>
+        <c:crossAx val="45724715"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2249,7 +2249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10597235"/>
+        <c:axId val="45724715"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2294,7 +2294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49414882"/>
+        <c:crossAx val="58233594"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2514,11 +2514,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74994498"/>
-        <c:axId val="27567947"/>
+        <c:axId val="24859104"/>
+        <c:axId val="48000448"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74994498"/>
+        <c:axId val="24859104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27567947"/>
+        <c:crossAx val="48000448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27567947"/>
+        <c:axId val="48000448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74994498"/>
+        <c:crossAx val="24859104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3176,11 +3176,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="80190542"/>
-        <c:axId val="35156513"/>
+        <c:axId val="55672778"/>
+        <c:axId val="59978640"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="80190542"/>
+        <c:axId val="55672778"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3213,7 +3213,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35156513"/>
+        <c:crossAx val="59978640"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3221,7 +3221,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="35156513"/>
+        <c:axId val="59978640"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3264,7 +3264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80190542"/>
+        <c:crossAx val="55672778"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3466,11 +3466,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19181690"/>
-        <c:axId val="10351145"/>
+        <c:axId val="74631850"/>
+        <c:axId val="7129836"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19181690"/>
+        <c:axId val="74631850"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3503,7 +3503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10351145"/>
+        <c:crossAx val="7129836"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3511,7 +3511,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10351145"/>
+        <c:axId val="7129836"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3555,7 +3555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19181690"/>
+        <c:crossAx val="74631850"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,11 +3763,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="21012645"/>
-        <c:axId val="65425080"/>
+        <c:axId val="66241013"/>
+        <c:axId val="41698179"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21012645"/>
+        <c:axId val="66241013"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3800,7 +3800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65425080"/>
+        <c:crossAx val="41698179"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3808,7 +3808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65425080"/>
+        <c:axId val="41698179"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3851,7 +3851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21012645"/>
+        <c:crossAx val="66241013"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4089,11 +4089,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="10380305"/>
-        <c:axId val="36849356"/>
+        <c:axId val="42827078"/>
+        <c:axId val="4819952"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10380305"/>
+        <c:axId val="42827078"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4126,7 +4126,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36849356"/>
+        <c:crossAx val="4819952"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4134,7 +4134,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36849356"/>
+        <c:axId val="4819952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10380305"/>
+        <c:crossAx val="42827078"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
@@ -2207,11 +2207,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="58233594"/>
-        <c:axId val="45724715"/>
+        <c:axId val="27892460"/>
+        <c:axId val="40148024"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="58233594"/>
+        <c:axId val="27892460"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2241,7 +2241,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45724715"/>
+        <c:crossAx val="40148024"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2249,7 +2249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45724715"/>
+        <c:axId val="40148024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2294,7 +2294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58233594"/>
+        <c:crossAx val="27892460"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2514,11 +2514,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24859104"/>
-        <c:axId val="48000448"/>
+        <c:axId val="61438070"/>
+        <c:axId val="54356334"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24859104"/>
+        <c:axId val="61438070"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48000448"/>
+        <c:crossAx val="54356334"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48000448"/>
+        <c:axId val="54356334"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24859104"/>
+        <c:crossAx val="61438070"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3176,11 +3176,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="55672778"/>
-        <c:axId val="59978640"/>
+        <c:axId val="65227012"/>
+        <c:axId val="21133550"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55672778"/>
+        <c:axId val="65227012"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3213,7 +3213,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59978640"/>
+        <c:crossAx val="21133550"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3221,7 +3221,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59978640"/>
+        <c:axId val="21133550"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3264,7 +3264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55672778"/>
+        <c:crossAx val="65227012"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3466,11 +3466,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74631850"/>
-        <c:axId val="7129836"/>
+        <c:axId val="23620810"/>
+        <c:axId val="29089931"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74631850"/>
+        <c:axId val="23620810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3503,7 +3503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7129836"/>
+        <c:crossAx val="29089931"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3511,7 +3511,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7129836"/>
+        <c:axId val="29089931"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3555,7 +3555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74631850"/>
+        <c:crossAx val="23620810"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,11 +3763,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="66241013"/>
-        <c:axId val="41698179"/>
+        <c:axId val="91127656"/>
+        <c:axId val="78532766"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66241013"/>
+        <c:axId val="91127656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3800,7 +3800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41698179"/>
+        <c:crossAx val="78532766"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3808,7 +3808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41698179"/>
+        <c:axId val="78532766"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3851,7 +3851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66241013"/>
+        <c:crossAx val="91127656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4089,11 +4089,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="42827078"/>
-        <c:axId val="4819952"/>
+        <c:axId val="71208387"/>
+        <c:axId val="70272808"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="42827078"/>
+        <c:axId val="71208387"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4126,7 +4126,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="4819952"/>
+        <c:crossAx val="70272808"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4134,7 +4134,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="4819952"/>
+        <c:axId val="70272808"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="42827078"/>
+        <c:crossAx val="71208387"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Band: Nascent</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 – &lt;1.8</t>
+    <t xml:space="preserve">1.0 – &lt;1.5</t>
   </si>
   <si>
     <t xml:space="preserve">Half-open bands; a pillar band in parentheses means judged, gap and held rows outnumber the levelled measured and documented ones.</t>
@@ -201,25 +201,25 @@
     <t xml:space="preserve">Band: Emerging</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8 – &lt;2.6</t>
+    <t xml:space="preserve">1.5 – &lt;2.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Established</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6 – &lt;3.4</t>
+    <t xml:space="preserve">2.5 – &lt;3.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Advanced</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4 – &lt;4.2</t>
+    <t xml:space="preserve">3.5 – &lt;4.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Transformative</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2 – 5.0</t>
+    <t xml:space="preserve">4.5 – 5.0</t>
   </si>
   <si>
     <t xml:space="preserve">Universal prerequisites</t>
@@ -2207,11 +2207,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="27892460"/>
-        <c:axId val="40148024"/>
+        <c:axId val="87839300"/>
+        <c:axId val="38913448"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="27892460"/>
+        <c:axId val="87839300"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2241,7 +2241,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40148024"/>
+        <c:crossAx val="38913448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2249,7 +2249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40148024"/>
+        <c:axId val="38913448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2294,7 +2294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27892460"/>
+        <c:crossAx val="87839300"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2514,11 +2514,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="61438070"/>
-        <c:axId val="54356334"/>
+        <c:axId val="40463317"/>
+        <c:axId val="20528083"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="61438070"/>
+        <c:axId val="40463317"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54356334"/>
+        <c:crossAx val="20528083"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="54356334"/>
+        <c:axId val="20528083"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61438070"/>
+        <c:crossAx val="40463317"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3176,11 +3176,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="65227012"/>
-        <c:axId val="21133550"/>
+        <c:axId val="31994990"/>
+        <c:axId val="16962870"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="65227012"/>
+        <c:axId val="31994990"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3213,7 +3213,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21133550"/>
+        <c:crossAx val="16962870"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3221,7 +3221,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21133550"/>
+        <c:axId val="16962870"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3264,7 +3264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65227012"/>
+        <c:crossAx val="31994990"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3466,11 +3466,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="23620810"/>
-        <c:axId val="29089931"/>
+        <c:axId val="83988355"/>
+        <c:axId val="30746618"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="23620810"/>
+        <c:axId val="83988355"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3503,7 +3503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29089931"/>
+        <c:crossAx val="30746618"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3511,7 +3511,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29089931"/>
+        <c:axId val="30746618"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3555,7 +3555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23620810"/>
+        <c:crossAx val="83988355"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,11 +3763,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="91127656"/>
-        <c:axId val="78532766"/>
+        <c:axId val="67885709"/>
+        <c:axId val="59102921"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="91127656"/>
+        <c:axId val="67885709"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3800,7 +3800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78532766"/>
+        <c:crossAx val="59102921"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3808,7 +3808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78532766"/>
+        <c:axId val="59102921"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3851,7 +3851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91127656"/>
+        <c:crossAx val="67885709"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4089,11 +4089,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="71208387"/>
-        <c:axId val="70272808"/>
+        <c:axId val="68826"/>
+        <c:axId val="29706307"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="71208387"/>
+        <c:axId val="68826"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4126,7 +4126,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70272808"/>
+        <c:crossAx val="29706307"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4134,7 +4134,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70272808"/>
+        <c:axId val="29706307"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71208387"/>
+        <c:crossAx val="68826"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11602,7 +11602,7 @@
         <v>3</v>
       </c>
       <c r="E66" s="9" t="str">
-        <f aca="false">IF($D66="","Not rated",IF((COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I66+$J66)&gt;($C66-COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D66&lt;1.8,"Nascent",IF($D66&lt;2.6,"Emerging",IF($D66&lt;3.4,"Established",IF($D66&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D66&lt;1.8,"Nascent",IF($D66&lt;2.6,"Emerging",IF($D66&lt;3.4,"Established",IF($D66&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D66="","Not rated",IF((COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I66+$J66)&gt;($C66-COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D66&lt;1.5,"Nascent",IF($D66&lt;2.5,"Emerging",IF($D66&lt;3.5,"Established",IF($D66&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D66&lt;1.5,"Nascent",IF($D66&lt;2.5,"Emerging",IF($D66&lt;3.5,"Established",IF($D66&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F66" s="15" t="n">
@@ -11647,7 +11647,7 @@
         <v>3.8</v>
       </c>
       <c r="E67" s="9" t="str">
-        <f aca="false">IF($D67="","Not rated",IF((COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I67+$J67)&gt;($C67-COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D67&lt;1.8,"Nascent",IF($D67&lt;2.6,"Emerging",IF($D67&lt;3.4,"Established",IF($D67&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D67&lt;1.8,"Nascent",IF($D67&lt;2.6,"Emerging",IF($D67&lt;3.4,"Established",IF($D67&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D67="","Not rated",IF((COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I67+$J67)&gt;($C67-COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D67&lt;1.5,"Nascent",IF($D67&lt;2.5,"Emerging",IF($D67&lt;3.5,"Established",IF($D67&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D67&lt;1.5,"Nascent",IF($D67&lt;2.5,"Emerging",IF($D67&lt;3.5,"Established",IF($D67&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Advanced</v>
       </c>
       <c r="F67" s="15" t="n">
@@ -11692,7 +11692,7 @@
         <v>2.88</v>
       </c>
       <c r="E68" s="9" t="str">
-        <f aca="false">IF($D68="","Not rated",IF((COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I68+$J68)&gt;($C68-COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D68&lt;1.8,"Nascent",IF($D68&lt;2.6,"Emerging",IF($D68&lt;3.4,"Established",IF($D68&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D68&lt;1.8,"Nascent",IF($D68&lt;2.6,"Emerging",IF($D68&lt;3.4,"Established",IF($D68&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D68="","Not rated",IF((COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I68+$J68)&gt;($C68-COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D68&lt;1.5,"Nascent",IF($D68&lt;2.5,"Emerging",IF($D68&lt;3.5,"Established",IF($D68&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D68&lt;1.5,"Nascent",IF($D68&lt;2.5,"Emerging",IF($D68&lt;3.5,"Established",IF($D68&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F68" s="15" t="n">
@@ -11737,7 +11737,7 @@
         <v>3.25</v>
       </c>
       <c r="E69" s="9" t="str">
-        <f aca="false">IF($D69="","Not rated",IF((COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I69+$J69)&gt;($C69-COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D69&lt;1.8,"Nascent",IF($D69&lt;2.6,"Emerging",IF($D69&lt;3.4,"Established",IF($D69&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D69&lt;1.8,"Nascent",IF($D69&lt;2.6,"Emerging",IF($D69&lt;3.4,"Established",IF($D69&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D69="","Not rated",IF((COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I69+$J69)&gt;($C69-COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D69&lt;1.5,"Nascent",IF($D69&lt;2.5,"Emerging",IF($D69&lt;3.5,"Established",IF($D69&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D69&lt;1.5,"Nascent",IF($D69&lt;2.5,"Emerging",IF($D69&lt;3.5,"Established",IF($D69&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F69" s="15" t="n">
@@ -11782,7 +11782,7 @@
         <v>3.33</v>
       </c>
       <c r="E70" s="9" t="str">
-        <f aca="false">IF($D70="","Not rated",IF((COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I70+$J70)&gt;($C70-COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D70&lt;1.8,"Nascent",IF($D70&lt;2.6,"Emerging",IF($D70&lt;3.4,"Established",IF($D70&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D70&lt;1.8,"Nascent",IF($D70&lt;2.6,"Emerging",IF($D70&lt;3.4,"Established",IF($D70&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D70="","Not rated",IF((COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I70+$J70)&gt;($C70-COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D70&lt;1.5,"Nascent",IF($D70&lt;2.5,"Emerging",IF($D70&lt;3.5,"Established",IF($D70&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D70&lt;1.5,"Nascent",IF($D70&lt;2.5,"Emerging",IF($D70&lt;3.5,"Established",IF($D70&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>(Established)</v>
       </c>
       <c r="F70" s="15" t="n">
@@ -11827,7 +11827,7 @@
         <v>3.11</v>
       </c>
       <c r="E71" s="9" t="str">
-        <f aca="false">IF($D71="","Not rated",IF((COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I71+$J71)&gt;($C71-COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D71&lt;1.8,"Nascent",IF($D71&lt;2.6,"Emerging",IF($D71&lt;3.4,"Established",IF($D71&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D71&lt;1.8,"Nascent",IF($D71&lt;2.6,"Emerging",IF($D71&lt;3.4,"Established",IF($D71&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D71="","Not rated",IF((COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I71+$J71)&gt;($C71-COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D71&lt;1.5,"Nascent",IF($D71&lt;2.5,"Emerging",IF($D71&lt;3.5,"Established",IF($D71&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D71&lt;1.5,"Nascent",IF($D71&lt;2.5,"Emerging",IF($D71&lt;3.5,"Established",IF($D71&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F71" s="15" t="n">
@@ -11872,7 +11872,7 @@
         <v>2.67</v>
       </c>
       <c r="E72" s="9" t="str">
-        <f aca="false">IF($D72="","Not rated",IF((COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I72+$J72)&gt;($C72-COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D72&lt;1.8,"Nascent",IF($D72&lt;2.6,"Emerging",IF($D72&lt;3.4,"Established",IF($D72&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D72&lt;1.8,"Nascent",IF($D72&lt;2.6,"Emerging",IF($D72&lt;3.4,"Established",IF($D72&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D72="","Not rated",IF((COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I72+$J72)&gt;($C72-COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D72&lt;1.5,"Nascent",IF($D72&lt;2.5,"Emerging",IF($D72&lt;3.5,"Established",IF($D72&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D72&lt;1.5,"Nascent",IF($D72&lt;2.5,"Emerging",IF($D72&lt;3.5,"Established",IF($D72&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F72" s="15" t="n">

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
@@ -180,7 +180,7 @@
     <t xml:space="preserve">Readiness threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">A use-case column whose bearing indicators average below this reads Partial.</t>
+    <t xml:space="preserve">A use-case column whose bearing indicators average below this reads Partial. Set to the Established band's lower edge.</t>
   </si>
   <si>
     <t xml:space="preserve">Leapfrog threshold</t>
@@ -2207,11 +2207,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="87839300"/>
-        <c:axId val="38913448"/>
+        <c:axId val="64120753"/>
+        <c:axId val="61067639"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="87839300"/>
+        <c:axId val="64120753"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2241,7 +2241,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38913448"/>
+        <c:crossAx val="61067639"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2249,7 +2249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38913448"/>
+        <c:axId val="61067639"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2294,7 +2294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87839300"/>
+        <c:crossAx val="64120753"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2514,11 +2514,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="40463317"/>
-        <c:axId val="20528083"/>
+        <c:axId val="94090183"/>
+        <c:axId val="84853301"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40463317"/>
+        <c:axId val="94090183"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20528083"/>
+        <c:crossAx val="84853301"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20528083"/>
+        <c:axId val="84853301"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40463317"/>
+        <c:crossAx val="94090183"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3176,11 +3176,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="31994990"/>
-        <c:axId val="16962870"/>
+        <c:axId val="86147475"/>
+        <c:axId val="65467860"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="31994990"/>
+        <c:axId val="86147475"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3213,7 +3213,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16962870"/>
+        <c:crossAx val="65467860"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3221,7 +3221,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16962870"/>
+        <c:axId val="65467860"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3264,7 +3264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31994990"/>
+        <c:crossAx val="86147475"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3466,11 +3466,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83988355"/>
-        <c:axId val="30746618"/>
+        <c:axId val="83703668"/>
+        <c:axId val="30714798"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83988355"/>
+        <c:axId val="83703668"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3503,7 +3503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30746618"/>
+        <c:crossAx val="30714798"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3511,7 +3511,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30746618"/>
+        <c:axId val="30714798"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3555,7 +3555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83988355"/>
+        <c:crossAx val="83703668"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,11 +3763,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="67885709"/>
-        <c:axId val="59102921"/>
+        <c:axId val="89221417"/>
+        <c:axId val="40250882"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67885709"/>
+        <c:axId val="89221417"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3800,7 +3800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59102921"/>
+        <c:crossAx val="40250882"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3808,7 +3808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="59102921"/>
+        <c:axId val="40250882"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3851,7 +3851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67885709"/>
+        <c:crossAx val="89221417"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4089,11 +4089,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="68826"/>
-        <c:axId val="29706307"/>
+        <c:axId val="2377752"/>
+        <c:axId val="64433423"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="68826"/>
+        <c:axId val="2377752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4126,7 +4126,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29706307"/>
+        <c:crossAx val="64433423"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4134,7 +4134,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="29706307"/>
+        <c:axId val="64433423"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68826"/>
+        <c:crossAx val="2377752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6193,7 +6193,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>47</v>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
@@ -1551,7 +1551,7 @@
     <t xml:space="preserve">Use case area</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean of bearing indicators</t>
+    <t xml:space="preserve">Mean of enabling indicators</t>
   </si>
   <si>
     <t xml:space="preserve">Blocking / limiting factor</t>
@@ -2207,11 +2207,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="64120753"/>
-        <c:axId val="61067639"/>
+        <c:axId val="99444205"/>
+        <c:axId val="83695379"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="64120753"/>
+        <c:axId val="99444205"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2241,7 +2241,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61067639"/>
+        <c:crossAx val="83695379"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2249,7 +2249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="61067639"/>
+        <c:axId val="83695379"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2294,7 +2294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64120753"/>
+        <c:crossAx val="99444205"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2514,11 +2514,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94090183"/>
-        <c:axId val="84853301"/>
+        <c:axId val="74788022"/>
+        <c:axId val="94583330"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94090183"/>
+        <c:axId val="74788022"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84853301"/>
+        <c:crossAx val="94583330"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84853301"/>
+        <c:axId val="94583330"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94090183"/>
+        <c:crossAx val="74788022"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3176,11 +3176,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="86147475"/>
-        <c:axId val="65467860"/>
+        <c:axId val="97000313"/>
+        <c:axId val="62104296"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86147475"/>
+        <c:axId val="97000313"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3213,7 +3213,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65467860"/>
+        <c:crossAx val="62104296"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3221,7 +3221,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65467860"/>
+        <c:axId val="62104296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3264,7 +3264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86147475"/>
+        <c:crossAx val="97000313"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3466,11 +3466,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83703668"/>
-        <c:axId val="30714798"/>
+        <c:axId val="83497202"/>
+        <c:axId val="55687198"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83703668"/>
+        <c:axId val="83497202"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3503,7 +3503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30714798"/>
+        <c:crossAx val="55687198"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3511,7 +3511,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30714798"/>
+        <c:axId val="55687198"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3555,7 +3555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83703668"/>
+        <c:crossAx val="83497202"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,11 +3763,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="89221417"/>
-        <c:axId val="40250882"/>
+        <c:axId val="40791958"/>
+        <c:axId val="1489377"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="89221417"/>
+        <c:axId val="40791958"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3800,7 +3800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40250882"/>
+        <c:crossAx val="1489377"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3808,7 +3808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40250882"/>
+        <c:axId val="1489377"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3851,7 +3851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89221417"/>
+        <c:crossAx val="40791958"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4089,11 +4089,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="2377752"/>
-        <c:axId val="64433423"/>
+        <c:axId val="7245119"/>
+        <c:axId val="10733034"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="2377752"/>
+        <c:axId val="7245119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4126,7 +4126,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64433423"/>
+        <c:crossAx val="10733034"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4134,7 +4134,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64433423"/>
+        <c:axId val="10733034"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2377752"/>
+        <c:crossAx val="7245119"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12189,8 +12189,8 @@
         <v>506</v>
       </c>
       <c r="B102" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(V$5:V$61,1,$T$5:$T$61),2),"")</f>
-        <v>3.27</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,V$5:V$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>3.3</v>
       </c>
       <c r="C102" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12206,8 +12206,8 @@
         <v>507</v>
       </c>
       <c r="B103" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(W$5:W$61,1,$T$5:$T$61),2),"")</f>
-        <v>3.12</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,W$5:W$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>3.21</v>
       </c>
       <c r="C103" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12223,8 +12223,8 @@
         <v>508</v>
       </c>
       <c r="B104" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(X$5:X$61,1,$T$5:$T$61),2),"")</f>
-        <v>3.13</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,X$5:X$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>3.35</v>
       </c>
       <c r="C104" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B104&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12240,8 +12240,8 @@
         <v>509</v>
       </c>
       <c r="B105" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(Y$5:Y$61,1,$T$5:$T$61),2),"")</f>
-        <v>3.22</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,Y$5:Y$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>3.33</v>
       </c>
       <c r="C105" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B105&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12257,8 +12257,8 @@
         <v>510</v>
       </c>
       <c r="B106" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(Z$5:Z$61,1,$T$5:$T$61),2),"")</f>
-        <v>3.03</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,Z$5:Z$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>3.25</v>
       </c>
       <c r="C106" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$92="Absent",$D$96="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$92="Unverified",$D$96="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$92="Present (narrow)",$D$96="Present (narrow)"),$B106&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12274,8 +12274,8 @@
         <v>511</v>
       </c>
       <c r="B107" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(AA$5:AA$61,1,$T$5:$T$61),2),"")</f>
-        <v>3.17</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,AA$5:AA$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>3.26</v>
       </c>
       <c r="C107" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$90="Absent",$D$91="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$90="Unverified",$D$91="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$90="Present (narrow)",$D$91="Present (narrow)",$D$97="Present (narrow)"),$B107&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Egypt.xlsx
@@ -234,10 +234,10 @@
     <t xml:space="preserve">AI-enabled services</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12 binds AGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruling pending ratification: the consent-and-rights prerequisite binds the agricultural-intelligence column.</t>
+    <t xml:space="preserve">7.12 binds ADV, SMF, FIN, AGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruling 13.4: the consent-and-rights prerequisite binds the agricultural-intelligence column.</t>
   </si>
   <si>
     <t xml:space="preserve">The shared ladder — scoring an indicator that is not a measurement</t>
@@ -1338,7 +1338,7 @@
     <t xml:space="preserve">AI</t>
   </si>
   <si>
-    <t xml:space="preserve">UC:AI</t>
+    <t xml:space="preserve">UC:ADV,SMF,FIN,AGI</t>
   </si>
   <si>
     <t xml:space="preserve">No agriculture/AI-specific consent or farmer-data-rights safeguards exist beyond the general regime. General regime now operational: PDPL 151/2020 became enforceable in practice with Executive Regulations issued by Minis</t>
@@ -1542,7 +1542,7 @@
     <t xml:space="preserve">Use case: ADV</t>
   </si>
   <si>
-    <t xml:space="preserve">Use case: AI-enabled (binds AGI)</t>
+    <t xml:space="preserve">Use case: personal or farm-level data (ADV, SMF, FIN, AGI)</t>
   </si>
   <si>
     <t xml:space="preserve">Use-case readiness  (feeds Playbook Step 2B — Digital Readiness)</t>
@@ -2207,11 +2207,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="99444205"/>
-        <c:axId val="83695379"/>
+        <c:axId val="8224733"/>
+        <c:axId val="58061644"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="99444205"/>
+        <c:axId val="8224733"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2241,7 +2241,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83695379"/>
+        <c:crossAx val="58061644"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2249,7 +2249,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83695379"/>
+        <c:axId val="58061644"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2294,7 +2294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99444205"/>
+        <c:crossAx val="8224733"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2514,11 +2514,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74788022"/>
-        <c:axId val="94583330"/>
+        <c:axId val="57561372"/>
+        <c:axId val="62042987"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74788022"/>
+        <c:axId val="57561372"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2551,7 +2551,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94583330"/>
+        <c:crossAx val="62042987"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2559,7 +2559,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="94583330"/>
+        <c:axId val="62042987"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2602,7 +2602,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74788022"/>
+        <c:crossAx val="57561372"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3176,11 +3176,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="97000313"/>
-        <c:axId val="62104296"/>
+        <c:axId val="51600024"/>
+        <c:axId val="46698804"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="97000313"/>
+        <c:axId val="51600024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3213,7 +3213,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62104296"/>
+        <c:crossAx val="46698804"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3221,7 +3221,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62104296"/>
+        <c:axId val="46698804"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3264,7 +3264,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97000313"/>
+        <c:crossAx val="51600024"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3466,11 +3466,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83497202"/>
-        <c:axId val="55687198"/>
+        <c:axId val="77182289"/>
+        <c:axId val="82011151"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83497202"/>
+        <c:axId val="77182289"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3503,7 +3503,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55687198"/>
+        <c:crossAx val="82011151"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3511,7 +3511,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55687198"/>
+        <c:axId val="82011151"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3555,7 +3555,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83497202"/>
+        <c:crossAx val="77182289"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3763,11 +3763,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="40791958"/>
-        <c:axId val="1489377"/>
+        <c:axId val="58123829"/>
+        <c:axId val="68632054"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40791958"/>
+        <c:axId val="58123829"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3800,7 +3800,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1489377"/>
+        <c:crossAx val="68632054"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3808,7 +3808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1489377"/>
+        <c:axId val="68632054"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3851,7 +3851,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40791958"/>
+        <c:crossAx val="58123829"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4089,11 +4089,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="7245119"/>
-        <c:axId val="10733034"/>
+        <c:axId val="83544096"/>
+        <c:axId val="29950205"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7245119"/>
+        <c:axId val="83544096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4126,7 +4126,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10733034"/>
+        <c:crossAx val="29950205"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4134,7 +4134,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10733034"/>
+        <c:axId val="29950205"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4177,7 +4177,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7245119"/>
+        <c:crossAx val="83544096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12193,12 +12193,12 @@
         <v>3.3</v>
       </c>
       <c r="C102" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
-        <v>Unverified</v>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)",$D$97="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <v>Blocked</v>
       </c>
       <c r="D102" s="10" t="str">
-        <f aca="false">IF($C102="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")),IF($B102&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
-        <v>2.1</v>
+        <f aca="false">IF($C102="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B102&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <v>2.1 7.12</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12210,12 +12210,12 @@
         <v>3.21</v>
       </c>
       <c r="C103" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
-        <v>Unverified</v>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$97="Present (narrow)"),$B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <v>Blocked</v>
       </c>
       <c r="D103" s="10" t="str">
-        <f aca="false">IF($C103="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")),IF($B103&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
-        <v>2.1</v>
+        <f aca="false">IF($C103="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B103&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <v>2.1 7.12</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12261,12 +12261,12 @@
         <v>3.25</v>
       </c>
       <c r="C106" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$92="Absent",$D$96="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$92="Unverified",$D$96="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$92="Present (narrow)",$D$96="Present (narrow)"),$B106&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
-        <v>Unverified</v>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$92="Absent",$D$96="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$92="Unverified",$D$96="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$92="Present (narrow)",$D$96="Present (narrow)",$D$97="Present (narrow)"),$B106&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <v>Blocked</v>
       </c>
       <c r="D106" s="10" t="str">
-        <f aca="false">IF($C106="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")),IF($B106&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
-        <v>2.1</v>
+        <f aca="false">IF($C106="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B106&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <v>2.1 7.12</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
